--- a/veterinary_service_forms/006_pangolin_rehabilitation_daily_report--veterinary_service_forms.xlsx
+++ b/veterinary_service_forms/006_pangolin_rehabilitation_daily_report--veterinary_service_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>care_provider</t>
+          <t>care_provider_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Care Provider</t>
+          <t>Care Provider 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pangolin ID</t>
+          <t>Pangolin Id Alt</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>species</t>
+          <t>species_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Species</t>
+          <t>Species 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>care_location</t>
+          <t>care_location_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Care Location</t>
+          <t>Care Location 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Care Location</t>
+          <t>Care Location Alt</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>medical_notes</t>
+          <t>medical_notes_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Medical Notes</t>
+          <t>Medical Notes 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>food_intake</t>
+          <t>food_intake_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Food Intake</t>
+          <t>Food Intake 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ASSIGNED_TOOL</t>
+          <t>ASSIGNED TOOL</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>care_provider_choices</t>
+          <t>care_provider_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1102,7 +1102,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>care_provider_choices</t>
+          <t>care_provider_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1153,7 +1153,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>species_choices</t>
+          <t>species_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1170,7 +1170,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>species_choices</t>
+          <t>species_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
